--- a/artfynd/A 32792-2025 artfynd.xlsx
+++ b/artfynd/A 32792-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>362423</v>
       </c>
       <c r="B2" t="n">
-        <v>90052</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537724.4622223554</v>
+        <v>537724</v>
       </c>
       <c r="R2" t="n">
-        <v>7095924.143361062</v>
+        <v>7095924</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2010-10-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2010-10-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119847218</v>
+        <v>119847343</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537688</v>
+        <v>537560</v>
       </c>
       <c r="R3" t="n">
-        <v>7096018</v>
+        <v>7095841</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -902,15 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119847271</v>
+        <v>377468</v>
       </c>
       <c r="B4" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,37 +893,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Järilån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537580</v>
+        <v>537459</v>
       </c>
       <c r="R4" t="n">
-        <v>7095997</v>
+        <v>7096028</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,12 +947,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2010-10-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2010-10-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,34 +961,37 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Elin Agerberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Elin Agerberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119847301</v>
+        <v>377469</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,19 +1017,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Järilån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>537521</v>
+        <v>537450</v>
       </c>
       <c r="R5" t="n">
-        <v>7095905</v>
+        <v>7095977</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1081,12 +1053,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2010-10-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2010-10-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,34 +1067,37 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Elin Agerberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Elin Agerberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119847172</v>
+        <v>119847301</v>
       </c>
       <c r="B6" t="n">
-        <v>74654</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,21 +1105,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>537701</v>
+        <v>537521</v>
       </c>
       <c r="R6" t="n">
-        <v>7095958</v>
+        <v>7095905</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1220,15 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119847173</v>
+        <v>119847205</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1263,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>537701</v>
+        <v>537688</v>
       </c>
       <c r="R7" t="n">
-        <v>7095958</v>
+        <v>7096017</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1326,37 +1296,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119847234</v>
+        <v>119847173</v>
       </c>
       <c r="B8" t="n">
-        <v>74654</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1369,10 +1334,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>537676</v>
+        <v>537701</v>
       </c>
       <c r="R8" t="n">
-        <v>7096022</v>
+        <v>7095958</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,37 +1397,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119847320</v>
+        <v>119847218</v>
       </c>
       <c r="B9" t="n">
-        <v>74654</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,10 +1435,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537531</v>
+        <v>537688</v>
       </c>
       <c r="R9" t="n">
-        <v>7095909</v>
+        <v>7096018</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1538,15 +1498,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119847205</v>
+        <v>119847172</v>
       </c>
       <c r="B10" t="n">
-        <v>82321</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,21 +1509,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537688</v>
+        <v>537701</v>
       </c>
       <c r="R10" t="n">
-        <v>7096017</v>
+        <v>7095958</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1644,15 +1599,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119847343</v>
+        <v>119847234</v>
       </c>
       <c r="B11" t="n">
-        <v>90576</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,21 +1610,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1687,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>537560</v>
+        <v>537676</v>
       </c>
       <c r="R11" t="n">
-        <v>7095841</v>
+        <v>7096022</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1753,12 +1703,7 @@
         <v>119847293</v>
       </c>
       <c r="B12" t="n">
-        <v>74654</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,15 +1801,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119847192</v>
+        <v>119847320</v>
       </c>
       <c r="B13" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,21 +1812,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1899,10 +1839,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537667</v>
+        <v>537531</v>
       </c>
       <c r="R13" t="n">
-        <v>7095989</v>
+        <v>7095909</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1959,6 +1899,107 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>119847192</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Järilån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>537667</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7095989</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32792-2025 artfynd.xlsx
+++ b/artfynd/A 32792-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/362423</t>
         </is>
       </c>
     </row>
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119847343</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/377468</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/377469</t>
         </is>
       </c>
     </row>
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119847301</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1293,6 +1323,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119847205</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1394,6 +1429,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119847173</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1495,6 +1535,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119847218</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1596,6 +1641,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119847172</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1697,6 +1747,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119847234</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1798,6 +1853,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119847293</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1899,6 +1959,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119847320</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2000,8 +2065,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119847192</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>